--- a/RFPNormaliser.xlsx
+++ b/RFPNormaliser.xlsx
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FieldMappings" displayName="FieldMappings" ref="A1:G261" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FieldMappings" displayName="FieldMappings" ref="A1:G267" headerRowCount="1">
   <autoFilter ref="A1:G261"/>
   <tableColumns count="7">
     <tableColumn id="1" name="SourceField"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClientProfiles" displayName="ClientProfiles" ref="A1:F2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClientProfiles" displayName="ClientProfiles" ref="A1:F1" headerRowCount="1">
   <autoFilter ref="A1:F2"/>
   <tableColumns count="6">
     <tableColumn id="1" name="ClientId"/>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProcessingLog" displayName="ProcessingLog" ref="A1:N2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProcessingLog" displayName="ProcessingLog" ref="A1:N1" headerRowCount="1">
   <autoFilter ref="A1:M2"/>
   <tableColumns count="13">
     <tableColumn id="1" name="LogId"/>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RowProcessingLog" displayName="RowProcessingLog" ref="A1:L2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RowProcessingLog" displayName="RowProcessingLog" ref="A1:L1" headerRowCount="1">
   <autoFilter ref="A1:L2"/>
   <tableColumns count="12">
     <tableColumn id="1" name="RowId"/>

--- a/RFPNormaliser.xlsx
+++ b/RFPNormaliser.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClientProfiles" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessingLog" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RowProcessingLog" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NormalisedOutputs" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -248,6 +249,58 @@
     <tableColumn id="10" name="Confidence"/>
     <tableColumn id="11" name="ReviewedBy"/>
     <tableColumn id="12" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NormalisedOutputs" displayName="NormalisedOutputs" ref="A1:AQ1" headerRowCount="1">
+  <autoFilter ref="A1:AQ1"/>
+  <tableColumns count="43">
+    <tableColumn id="1" name="Equipment ID"/>
+    <tableColumn id="2" name="Bid Number"/>
+    <tableColumn id="3" name="Asset Tag"/>
+    <tableColumn id="4" name="Alt Control Number"/>
+    <tableColumn id="5" name="Master ID"/>
+    <tableColumn id="6" name="Device Description"/>
+    <tableColumn id="7" name="Device Type"/>
+    <tableColumn id="8" name="Make"/>
+    <tableColumn id="9" name="Manufacturer"/>
+    <tableColumn id="10" name="Model Name"/>
+    <tableColumn id="11" name="Model Number"/>
+    <tableColumn id="12" name="Serial Number"/>
+    <tableColumn id="13" name="Modality"/>
+    <tableColumn id="14" name="Facility Name"/>
+    <tableColumn id="15" name="System Name"/>
+    <tableColumn id="16" name="Building Name"/>
+    <tableColumn id="17" name="Department"/>
+    <tableColumn id="18" name="Sub Location"/>
+    <tableColumn id="19" name="Status"/>
+    <tableColumn id="20" name="In Service Date"/>
+    <tableColumn id="21" name="Date Added"/>
+    <tableColumn id="22" name="Warranty Expiration Date"/>
+    <tableColumn id="23" name="Agreement Expiration Date"/>
+    <tableColumn id="24" name="Coverage Template"/>
+    <tableColumn id="25" name="Coverage Level"/>
+    <tableColumn id="26" name="Service Model"/>
+    <tableColumn id="27" name="Service Times"/>
+    <tableColumn id="28" name="Incumbent Provider"/>
+    <tableColumn id="29" name="Contract Reference"/>
+    <tableColumn id="30" name="Special Provisions"/>
+    <tableColumn id="31" name="Early Out"/>
+    <tableColumn id="32" name="Early Out Notes"/>
+    <tableColumn id="33" name="Component Flag"/>
+    <tableColumn id="34" name="In Current Inventory"/>
+    <tableColumn id="35" name="Internal Notes"/>
+    <tableColumn id="36" name="External Notes"/>
+    <tableColumn id="37" name="Source Tab"/>
+    <tableColumn id="38" name="Source Format"/>
+    <tableColumn id="39" name="Client Name"/>
+    <tableColumn id="40" name="Source Format"/>
+    <tableColumn id="41" name="Date Processed"/>
+    <tableColumn id="42" name="Processed By"/>
+    <tableColumn id="43" name="Log ID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15776,4 +15829,283 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AQ1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Equipment ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Bid Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Asset Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Alt Control Number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Master ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Device Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Device Type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Model Name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Model Number</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Serial Number</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Facility Name</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Building Name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Sub Location</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>In Service Date</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Date Added</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Warranty Expiration Date</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Agreement Expiration Date</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage Template</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage Level</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Service Model</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Service Times</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Incumbent Provider</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Contract Reference</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Special Provisions</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Early Out</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Early Out Notes</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Component Flag</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>In Current Inventory</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Internal Notes</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>External Notes</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Source Tab</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Source Format</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Client Name</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Source Format</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Date Processed</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Processed By</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Log ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>